--- a/ai_logs/nghia_log_2.xlsx
+++ b/ai_logs/nghia_log_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daomi\.gemini\antigravity\scratch\Food_delivery-main\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B33911-6433-461A-B820-AEDADFC38F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EC394B-AF0C-4993-977B-6D3FFCCAB13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="192">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -287,9 +287,6 @@
     <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
   </si>
   <si>
-    <t>☐</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -408,9 +405,6 @@
 </t>
   </si>
   <si>
-    <t>gnoring the AI's advice, I implemented the `synchronized` keyword myself, adding it to the `writeLineToCsv()` method in the `BaseCsvRepository` class to force threads to queue sequentially when writing to the file.</t>
-  </si>
-  <si>
     <t>When I ran the Simulator Tool with 50 concurrent threads, I opened the orders.csv file and found that some data lines were fused together or had half of their information missing.</t>
   </si>
   <si>
@@ -424,9 +418,6 @@
   </si>
   <si>
     <t>ArrayList in Java is NOT thread-safe. If thread A is iterating through the list to find a driver, and thread B updates the status or adds a new driver to the list, Java will immediately throw a ConcurrentModificationException, causing the program to crash.</t>
-  </si>
-  <si>
-    <t>pointed out this error to the AI ​​and asked them to rewrite it. Ultimately, I decided to change the ArrayList to a CopyOnWriteArrayList (part of the `java.util.concurrent` package) to ensure safety when multiple threads are simultaneously reading/writing the driver list.</t>
   </si>
   <si>
     <t xml:space="preserve"> I copied the AI's code and ran a simulation, and the program immediately threw an exception (Exception stack trace) in the console with the line `java.util.ConcurrentModificationException` in the driver search code.</t>
@@ -576,6 +567,66 @@
   </si>
   <si>
     <t>Multi-threading and Generic</t>
+  </si>
+  <si>
+    <t>Gnoring the AI's advice, I implemented the `synchronized` keyword myself, adding it to the `writeLineToCsv()` method in the `BaseCsvRepository` class to force threads to queue sequentially when writing to the file.</t>
+  </si>
+  <si>
+    <t>Pointed out this error to the AI ​​and asked them to rewrite it. Ultimately, I decided to change the ArrayList to a CopyOnWriteArrayList (part of the `java.util.concurrent` package) to ensure safety when multiple threads are simultaneously reading/writing the driver list.</t>
+  </si>
+  <si>
+    <t>☑</t>
+  </si>
+  <si>
+    <t>Xác định được nguyên nhân gây crash app khi xử lý file lớn và chốt phương án fix.</t>
+  </si>
+  <si>
+    <t>Giúp tách biệt phần UI và Logic (áp dụng MVC) thay vì viết chung như ý định ban đầu.</t>
+  </si>
+  <si>
+    <t>Không dùng code AI gen ra hoàn toàn vì AI dùng thư viện cũ, chỉ tham khảo thuật toán cốt lõi.</t>
+  </si>
+  <si>
+    <t>Code implement tại file src/services/AuthService.ts.</t>
+  </si>
+  <si>
+    <t>Chỉ lấy ý tưởng phân chia component của AI, tự viết lại toàn bộ CSS bằng Tailwind cho đúng design system.</t>
+  </si>
+  <si>
+    <t>Ghi tổng số lượng entry (bản ghi/prompt) thực tế bạn đã làm trong file log.</t>
+  </si>
+  <si>
+    <t>Ghi số lượng hoặc tỉ lệ component đã được cover prompt trên tổng số component của project.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ghi số lượng lỗi ảo giác (hallucination) thực tế của AI mà bạn đã phát hiện và ghi nhận lại được.</t>
+  </si>
+  <si>
+    <t>Ghi tỉ lệ hoặc số lượng entry bạn đã điền đủ phần Human Delta (trả lời đủ các câu hỏi phản biện).</t>
+  </si>
+  <si>
+    <t>Tính toán và ghi tỉ lệ phần trăm (%) thực tế số entry có kèm theo bằng chứng (link commit, ảnh chụp màn hình, biểu đồ,...).</t>
+  </si>
+  <si>
+    <t>Chọn JWT thay vì Session để dễ scale cho microservices sau này. Bỏ qua gợi ý dùng LocalStorage của AI vì sợ XSS, chọn lưu vào httpOnly cookie.</t>
+  </si>
+  <si>
+    <t>Có</t>
+  </si>
+  <si>
+    <t>Ở file auth.ts dòng 45.</t>
+  </si>
+  <si>
+    <t>Junit là cái gì? Nó ảnh hưởng như thế nào đến project này? Nếu không dùng thì có ảnh hưởng như thế nào?</t>
+  </si>
+  <si>
+    <t>JUnit là một framework phổ biến nhất dùng để viết và chạy Unit Test (kiểm thử mức đơn vị) cho ngôn ngữ Java. Nó giúp lập trình viên tự động hóa việc kiểm tra xem từng hàm (function), từng class trong code có hoạt động đúng như mong đợi hay không.</t>
+  </si>
+  <si>
+    <t>Test hoàn toàn bằng tay (chạy app lên, bấm thử từng nút, nhập thử từng luồng dữ liệu). Việc này cực kỳ mất thời gian, rất dễ bỏ sót lỗi (human error) và khi project lớn lên, việc bảo trì (maintain) code sẽ trở thành ác mộng vì không ai dám sửa code cũ sợ làm hỏng hệ thống.</t>
+  </si>
+  <si>
+    <t>Đảm bảo chất lượng code. Khi bạn thêm tính năng mới hoặc sửa code cũ (refactor), JUnit sẽ tự động chạy lại các test cases để đảm bảo bạn không làm hỏng những thứ đang chạy tốt. Nó là "tấm khiên" bảo vệ project khỏi những lỗi tiềm ẩn (bugs).</t>
   </si>
 </sst>
 </file>
@@ -585,7 +636,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -666,6 +717,17 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -731,7 +793,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -771,10 +833,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -784,10 +852,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1103,60 +1174,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -1164,7 +1235,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C11" s="3">
         <v>10</v>
@@ -1225,16 +1296,16 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1342,28 +1413,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1426,16 +1497,16 @@
         <v>7</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="H5" s="7"/>
     </row>
@@ -1450,16 +1521,16 @@
         <v>9</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>137</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="H6" s="7"/>
     </row>
@@ -1474,16 +1545,16 @@
         <v>5</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="H7" s="7"/>
     </row>
@@ -1498,16 +1569,16 @@
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>148</v>
       </c>
       <c r="H8" s="7"/>
     </row>
@@ -1519,19 +1590,19 @@
         <v>8</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="G9" s="7" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -1543,19 +1614,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>127</v>
-      </c>
       <c r="G10" s="7" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1564,22 +1635,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>154</v>
       </c>
       <c r="H11" s="7"/>
     </row>
@@ -1588,22 +1659,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="H12" s="7"/>
     </row>
@@ -1612,33 +1683,47 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>171</v>
-      </c>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="A14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>191</v>
+      </c>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1766,7 +1851,9 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1781,24 +1868,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1825,19 +1912,19 @@
         <v>6</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="216" x14ac:dyDescent="0.3">
@@ -1845,19 +1932,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
@@ -1865,23 +1952,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>165</v>
-      </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
+      <c r="A7" s="7">
+        <v>11</v>
+      </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2116,20 +2205,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2150,69 +2239,79 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="13"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>90</v>
-      </c>
       <c r="C10" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="13"/>
+        <v>174</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -2226,92 +2325,102 @@
         <v>78</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>80</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="C15" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="13" t="s">
+      <c r="C16" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="C17" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="13"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>97</v>
-      </c>
       <c r="C18" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="13"/>
+        <v>174</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2319,22 +2428,28 @@
         <v>34</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="D27" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="B28" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
